--- a/order_forms/046_tax_software_package_selection--order_forms.xlsx
+++ b/order_forms/046_tax_software_package_selection--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -515,23 +515,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>tax_software_package_selection_form</t>
+          <t>tax_professional</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tax software package selection</t>
+          <t>Tax Professional</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -543,41 +543,41 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>buyer_preferences</t>
+          <t>tax_professional_experience</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>buyer preferences</t>
+          <t>Professional Experience</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>package_type</t>
+          <t>tax_package_features</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>package type</t>
+          <t>Package Features</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,110 +589,110 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tax_professional</t>
+          <t>package_benefits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tax professional</t>
+          <t>Benefits</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>tax_professional_experience</t>
+          <t>software_seller</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tax professional experience</t>
+          <t>Software Seller</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>tax_package_features</t>
+          <t>confidence_level</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tax package features</t>
+          <t>Confidence Level</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>software_seller</t>
+          <t>hours_spent</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>software seller</t>
+          <t>Hours Spent</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>faster_data_collection</t>
+          <t>expected_date_of_purchase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>faster data collection</t>
+          <t>Expected Date of Purchase</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -704,386 +704,87 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>smoother_online_purchases</t>
+          <t>payment_method</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>smoother online purchases</t>
+          <t>Payment Method</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>customer_support</t>
+          <t>purchases_count</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>customer support</t>
+          <t>Purchases Count</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>online_purchases</t>
+          <t>hours_spent_per_month</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>online purchases</t>
+          <t>Hours Spent per Month</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tax_software_package_selection_form</t>
+          <t>expected_date_of_purchase_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tax software package selection</t>
+          <t>Expected Date Of Purchase 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>buyer_preferences</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>buyer preferences</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>package_type</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>package type</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>tax_professional</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>tax professional</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>tax_professional_experience</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>tax professional experience</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>tax_package_features</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>tax package features</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>software_seller</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>software seller</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>faster_data_collection</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>faster data collection</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>smoother_online_purchases</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>smoother online purchases</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>customer_support</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>customer support</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>online_purchases</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>online purchases</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>tax_software_package_selection_form</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>tax software package selection</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>buyer_preferences</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>buyer preferences</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>package_type</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>package type</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C51"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1126,170 +827,170 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tax_software_package_selection_form_choices</t>
+          <t>tax_professional_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tax_consultant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tax Consultant</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tax_software_package_selection_form_choices</t>
+          <t>tax_professional_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tax_lawyer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tax Lawyer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>buyer_preferences_choices</t>
+          <t>tax_professional_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tax_accountant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tax Accountant</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>buyer_preferences_choices</t>
+          <t>tax_professional_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tax_advisor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tax Advisor</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>package_type_choices</t>
+          <t>tax_professional_experience_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>0-5_years</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>0-5 years</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>package_type_choices</t>
+          <t>tax_professional_experience_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>5-10_years</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>5-10 years</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>tax_professional_choices</t>
+          <t>tax_professional_experience_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>10-20_years</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>10-20 years</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tax_professional_choices</t>
+          <t>tax_professional_experience_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>20_years_+</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>20 years +</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>tax_professional_experience_choices</t>
+          <t>tax_package_features_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fast_and_efficient_data_collection</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fast and efficient data collection</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>tax_professional_experience_choices</t>
+          <t>tax_package_features_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>smoother_online_purchases</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Smoother online purchases</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1002,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good_customer_support</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good customer support</t>
         </is>
       </c>
     </row>
@@ -1318,658 +1019,199 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online_purchases_available</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online purchases available</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>software_seller_choices</t>
+          <t>package_benefits_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>fast_and_efficient_data_collection</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Fast and efficient data collection</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>software_seller_choices</t>
+          <t>package_benefits_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>smoother_online_purchases</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Smoother online purchases</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>faster_data_collection_choices</t>
+          <t>package_benefits_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>good_customer_support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Good customer support</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>faster_data_collection_choices</t>
+          <t>package_benefits_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>online_purchases_available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Online purchases available</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>smoother_online_purchases_choices</t>
+          <t>software_seller_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>highly_rated</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Highly rated</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>smoother_online_purchases_choices</t>
+          <t>software_seller_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>software_seller_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>low_rated</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Low rated</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>customer_support_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>online_purchases_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>online_purchases_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>tax_software_package_selection_form_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>tax_software_package_selection_form_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>buyer_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>buyer_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>package_type_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>package_type_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>tax_professional_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>tax_professional_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>tax_professional_experience_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>tax_professional_experience_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>tax_package_features_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>tax_package_features_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>software_seller_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>software_seller_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>faster_data_collection_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>faster_data_collection_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>smoother_online_purchases_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>smoother_online_purchases_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>customer_support_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>customer_support_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>online_purchases_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>online_purchases_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>tax_software_package_selection_form_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>tax_software_package_selection_form_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>buyer_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>buyer_preferences_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>package_type_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>package_type_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
